--- a/rules/CORE-000706/positive/01/data/unit-test-coreid-FB0906-positive.xlsx
+++ b/rules/CORE-000706/positive/01/data/unit-test-coreid-FB0906-positive.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Library" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ae.xpt" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="cm.xpt" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="mh.xpt" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Library" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ae.xpt" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cm.xpt" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mh.xpt" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -532,12 +532,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Filename</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Label</t>
         </is>
